--- a/Trabalho_2/dados/normal/primeiroteste_helicenormal.xlsx
+++ b/Trabalho_2/dados/normal/primeiroteste_helicenormal.xlsx
@@ -4708,11 +4708,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="57150837"/>
-        <c:axId val="36251497"/>
+        <c:axId val="264834"/>
+        <c:axId val="11187731"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="57150837"/>
+        <c:axId val="264834"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4778,7 +4778,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36251497"/>
+        <c:crossAx val="11187731"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4786,7 +4786,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36251497"/>
+        <c:axId val="11187731"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4862,7 +4862,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57150837"/>
+        <c:crossAx val="264834"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9392,11 +9392,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="69630410"/>
-        <c:axId val="1437127"/>
+        <c:axId val="83670437"/>
+        <c:axId val="31641813"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69630410"/>
+        <c:axId val="83670437"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9462,7 +9462,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1437127"/>
+        <c:crossAx val="31641813"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9470,7 +9470,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1437127"/>
+        <c:axId val="31641813"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9546,7 +9546,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69630410"/>
+        <c:crossAx val="83670437"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14076,11 +14076,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="19914583"/>
-        <c:axId val="48742397"/>
+        <c:axId val="15168714"/>
+        <c:axId val="8296523"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="19914583"/>
+        <c:axId val="15168714"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14146,7 +14146,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48742397"/>
+        <c:crossAx val="8296523"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14154,7 +14154,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48742397"/>
+        <c:axId val="8296523"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14230,7 +14230,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19914583"/>
+        <c:crossAx val="15168714"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14307,9 +14307,11 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
+    <cs:lineWidthScale>1</cs:lineWidthScale>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
+    <a:defRPr sz="1800" b="0"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -14517,9 +14519,11 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
+    <cs:lineWidthScale>1</cs:lineWidthScale>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
+    <a:defRPr sz="1800" b="0"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -14727,9 +14731,11 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
+    <cs:lineWidthScale>1</cs:lineWidthScale>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
+    <a:defRPr sz="1800" b="0"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -14944,9 +14950,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>263520</xdr:colOff>
+      <xdr:colOff>263160</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>74160</xdr:rowOff>
+      <xdr:rowOff>73800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14955,7 +14961,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5361480" y="190440"/>
-        <a:ext cx="4516560" cy="2741400"/>
+        <a:ext cx="4516200" cy="2741040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14974,9 +14980,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>263520</xdr:colOff>
+      <xdr:colOff>263160</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>74160</xdr:rowOff>
+      <xdr:rowOff>73800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14985,7 +14991,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5361480" y="3238560"/>
-        <a:ext cx="4516560" cy="2741040"/>
+        <a:ext cx="4516200" cy="2740680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -15004,9 +15010,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>263520</xdr:colOff>
+      <xdr:colOff>263160</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>74160</xdr:rowOff>
+      <xdr:rowOff>73800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -15015,7 +15021,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5361480" y="6286680"/>
-        <a:ext cx="4516560" cy="2741040"/>
+        <a:ext cx="4516200" cy="2740680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -15216,7 +15222,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
